--- a/角色列表.xlsx
+++ b/角色列表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="1314">
   <si>
     <t/>
   </si>
@@ -4080,6 +4080,26 @@
   </si>
   <si>
     <t>璃月古代辞赋中不乏对于「琉璃百合」的溢美，但它现今却近乎灭绝，只在「玉京台」还有保留。名声在外却又不可多得，因此更加价格不菲。</t>
+  </si>
+  <si>
+    <t>（李）</t>
+  </si>
+  <si>
+    <t>（¿李）</t>
+  </si>
+  <si>
+    <t>（¿莫）</t>
+  </si>
+  <si>
+    <t>【「吾以己心代天心新」】
+士气打击+15%</t>
+  </si>
+  <si>
+    <t>【「吾以己心代天心」】
+士气打击+15%</t>
+  </si>
+  <si>
+    <t>（温亨廷）</t>
   </si>
 </sst>
 </file>
@@ -4999,14 +5019,14 @@
     <col min="2" max="2" width="3.23438" customWidth="1"/>
     <col min="3" max="3" width="3.91406" customWidth="1"/>
     <col min="4" max="4" width="16.1836" style="4" customWidth="1"/>
-    <col min="5" max="6" width="19.4219" style="4" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="9.44141" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.1836" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="1.61328" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="64.7422" style="12" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="28.3242" style="12" hidden="1" customWidth="1"/>
-    <col min="13" max="16" width="3.64062" style="12" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="22.2539" style="5" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="19.4219" style="4" customWidth="1"/>
+    <col min="7" max="8" width="9.44141" customWidth="1"/>
+    <col min="9" max="9" width="16.1836" customWidth="1"/>
+    <col min="10" max="10" width="1.61328" customWidth="1"/>
+    <col min="11" max="11" width="64.7422" style="12" customWidth="1"/>
+    <col min="12" max="12" width="28.3242" style="12" customWidth="1"/>
+    <col min="13" max="16" width="3.64062" style="12" customWidth="1"/>
+    <col min="17" max="17" width="22.2539" style="5" customWidth="1"/>
     <col min="18" max="18" width="47.4844" style="12" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="49.5039" style="12" customWidth="1"/>
     <col min="20" max="20" width="11.8711" style="12" customWidth="1"/>
@@ -6811,7 +6831,7 @@
         <v>335</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>278</v>
+        <v>1309</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>336</v>
@@ -6917,7 +6937,7 @@
         <v>354</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>355</v>
+        <v>1310</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>356</v>
@@ -9785,7 +9805,7 @@
         <v>865</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>866</v>
+        <v>1313</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>867</v>
@@ -11827,7 +11847,7 @@
         <v>6</v>
       </c>
       <c r="Q124" s="85" t="s">
-        <v>1298</v>
+        <v>1312</v>
       </c>
       <c r="R124" s="34" t="s"/>
       <c r="S124" s="34" t="s">
